--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.9</v>
+        <v>0.904</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>56.52</v>
+        <v>52.53</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.978</v>
+        <v>0.991</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0492199993133545</v>
+        <v>0.05293000221252441</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52357765.88818117</v>
+        <v>52357760.36550543</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>56.52</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2959260928</v>
+        <v>2750353152</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>8.359999999999999</v>
+        <v>7.77</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.67</v>
+        <v>6.37</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="6">
@@ -1532,14 +1532,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4480798208</v>
+        <v>4401627136</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>13.454</v>
+        <v>13.349</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.641</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="7">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4483996160</v>
+        <v>4231762432</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>25.20486</v>
+        <v>23.787037</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>8.470000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.366</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
@@ -1578,14 +1578,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>4518517248</v>
+        <v>3829841408</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.711</v>
+        <v>21.075</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.853</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="9">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>5828441088</v>
+        <v>5982076416</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>22.92972</v>
+        <v>23.534136</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>16.947</v>
+        <v>16.859</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.452</v>
+        <v>1.445</v>
       </c>
     </row>
     <row r="10">
@@ -1624,16 +1624,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6484491264</v>
+        <v>6485249024</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>19.27106</v>
+        <v>19.273314</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>11.35</v>
+        <v>11.285</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>1.855</v>
+        <v>1.845</v>
       </c>
     </row>
     <row r="11">
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>79451224</v>
+        <v>77749632</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>0.30859178</v>
+        <v>0.30198273</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>-1.962</v>
+        <v>-1.97</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.051</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="12">
@@ -1673,13 +1673,13 @@
       </c>
       <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>28.67633</v>
+        <v>30.030193</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.104</v>
+        <v>16.445</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.83</v>
+        <v>1.868</v>
       </c>
     </row>
     <row r="13">
@@ -1694,16 +1694,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>4759054848</v>
+        <v>4718024704</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>14.870286</v>
+        <v>15.440758</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>1.688</v>
+        <v>1.701</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>1.021</v>
+        <v>1.029</v>
       </c>
     </row>
     <row r="15">
